--- a/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,710 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01M07XPBPWNNF8259W987H2FY7</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBPWNNF8259W987H2FY7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQ87Z2GNRAA55J1M5VX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQ87Z2GNRAA55J1M5VX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQFY35XJTXK4T2G3GSJ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQFY35XJTXK4T2G3GSJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQFP9XVTA3ZG6NMDE9V</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQFP9XVTA3ZG6NMDE9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQJB16K19BE5Y2N8T9B</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQJB16K19BE5Y2N8T9B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQNBBJFV795KDEG7ZDB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQNBBJFV795KDEG7ZDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQPNTTBPMC6FJTTMC2J</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQPNTTBPMC6FJTTMC2J</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQQFMVXKZ9JMRQRK2X6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQQFMVXKZ9JMRQRK2X6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQRY8G7A3A725QBS6T8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQRY8G7A3A725QBS6T8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Manage Users</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQWVBX2PM748YZ5AFKK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQWVBX2PM748YZ5AFKK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADP Workforce Now Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01M07XPBQXT7122P03WY828ZQB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQXT7122P03WY828ZQB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Create User Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M07XPBR0DZDW5PBPTTBRDH3Q</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR0DZDW5PBPTTBRDH3Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Update User Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M07XPBR2NXFDFZZEE8AW3B7T</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR2NXFDFZZEE8AW3B7T</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Delete User Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M07XPBR4FAB5V7RCXJ1H1MQV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR4FAB5V7RCXJ1H1MQV</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HCHB Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M07XPBR9ABD4TN06R94ZHZG1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR9ABD4TN06R94ZHZG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRCRJGPAGR97HFTTPDF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRCRJGPAGR97HFTTPDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Welcome Email Notification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRC91NSYEFYQ33336CS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRC91NSYEFYQ33336CS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Execution Success Notification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRG03CT1CHKH5BH1PPM</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRG03CT1CHKH5BH1PPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Execution Failure Notification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRJ7KMRDBH69CT69JSH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRJ7KMRDBH69CT69JSH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hard Coded Values</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSGQHTWJCR1P1AGVYBT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSGQHTWJCR1P1AGVYBT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSWXDM0YR37VFMPEW43</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSWXDM0YR37VFMPEW43</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01M07XPBT3TZP8EMNJ9RMVC6V3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT3TZP8EMNJ9RMVC6V3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01M07XPBT6H1X3NTYWPRF87AFN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6H1X3NTYWPRF87AFN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">

--- a/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01M07XPBPWNNF8259W987H2FY7</t>
+          <t>h_01M0AAEYKS1RCESPQR7M8VFYD1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBPWNNF8259W987H2FY7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYKS1RCESPQR7M8VFYD1</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01M07XPBQ87Z2GNRAA55J1M5VX</t>
+          <t>h_01M0AAEYMNZD5HSV2RJRHH68Q7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQ87Z2GNRAA55J1M5VX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYMNZD5HSV2RJRHH68Q7</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01M07XPBQQFMVXKZ9JMRQRK2X6</t>
+          <t>h_01M0AAEYNTDZDZGDVX4F15ACB5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQQFMVXKZ9JMRQRK2X6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYNTDZDZGDVX4F15ACB5</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01M07XPBQRY8G7A3A725QBS6T8</t>
+          <t>h_01M0AAEYNZ0GWPY28BY3A34JZK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBQRY8G7A3A725QBS6T8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYNZ0GWPY28BY3A34JZK</t>
         </is>
       </c>
     </row>
@@ -991,29 +991,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hard Coded Values</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M07XPBSGQHTWJCR1P1AGVYBT</t>
+          <t>h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSGQHTWJCR1P1AGVYBT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+          <t>h_01M07XPBSWXDM0YR37VFMPEW43</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSWXDM0YR37VFMPEW43</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,63 +1045,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M07XPBSWXDM0YR37VFMPEW43</t>
+          <t>h_01M07XPBSZZAW2ZV09YB23QDHR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSWXDM0YR37VFMPEW43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSZZAW2ZV09YB23QDHR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+          <t>h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M07XPBT3TZP8EMNJ9RMVC6V3</t>
+          <t>h_01M07XPBT6CHP3J1R72QFFA8VE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT3TZP8EMNJ9RMVC6V3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6CHP3J1R72QFFA8VE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,34 +1111,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+          <t>h_01M0AAEYTQZDBVE2XPYEPS1WKS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6CHP3J1R72QFFA8VE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h_01M07XPBT6H1X3NTYWPRF87AFN</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6H1X3NTYWPRF87AFN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYTQZDBVE2XPYEPS1WKS</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,73 +705,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Create User Settings</t>
+          <t>HCHB Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M07XPBR0DZDW5PBPTTBRDH3Q</t>
+          <t>h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR0DZDW5PBPTTBRDH3Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Update User Settings</t>
+          <t>User Provisioning Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01M07XPBR2NXFDFZZEE8AW3B7T</t>
+          <t>h_01M1GPY7NZQX0RZ0PMG8F2W1BW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR2NXFDFZZEE8AW3B7T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M1GPY7NZQX0RZ0PMG8F2W1BW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Delete User Settings</t>
+          <t>Create User Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01M07XPBR4FAB5V7RCXJ1H1MQV</t>
+          <t>h_01M1GQK0YZQPCWB3YWJRDS3JDB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR4FAB5V7RCXJ1H1MQV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M1GQK0YZQPCWB3YWJRDS3JDB</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HCHB Settings</t>
+          <t>Update User Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
+          <t>h_01M1GQK0Z0SG6XKKJWFP1NNJJ5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR84ZH48YVE2ZY4YQ4D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M1GQK0Z0SG6XKKJWFP1NNJJ5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Terminate User Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01M07XPBR9ABD4TN06R94ZHZG1</t>
+          <t>h_01M1GQK0Z19Q1JH7E484KHY074</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR9ABD4TN06R94ZHZG1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M1GQK0Z19Q1JH7E484KHY074</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01M07XPBRCRJGPAGR97HFTTPDF</t>
+          <t>h_01M07XPBR9ABD4TN06R94ZHZG1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRCRJGPAGR97HFTTPDF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBR9ABD4TN06R94ZHZG1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Welcome Email Notification</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01M07XPBRC91NSYEFYQ33336CS</t>
+          <t>h_01M07XPBRCRJGPAGR97HFTTPDF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRC91NSYEFYQ33336CS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRCRJGPAGR97HFTTPDF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Welcome Email Notification</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
+          <t>h_01M07XPBRC91NSYEFYQ33336CS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRC91NSYEFYQ33336CS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execution Success Notification</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01M07XPBRG03CT1CHKH5BH1PPM</t>
+          <t>h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRG03CT1CHKH5BH1PPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRFR9QNMF0WRJ5Z5XVJ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Execution Failure Notification</t>
+          <t>Execution Success Notification</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01M07XPBRJ7KMRDBH69CT69JSH</t>
+          <t>h_01M07XPBRG03CT1CHKH5BH1PPM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRJ7KMRDBH69CT69JSH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRG03CT1CHKH5BH1PPM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Execution Failure Notification</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
+          <t>h_01M07XPBRJ7KMRDBH69CT69JSH</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRJ7KMRDBH69CT69JSH</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
+          <t>h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBRYR1FG1S8BYH7PXR8M</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
+          <t>h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSA6TFBVPTYJDJ4SBMW</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+          <t>h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSEJ8S6TJK81Q9D6H2S</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01M07XPBSWXDM0YR37VFMPEW43</t>
+          <t>h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSWXDM0YR37VFMPEW43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSP2XQZC1FB2BQPMQS4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+          <t>h_01M07XPBSWXDM0YR37VFMPEW43</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSZZAW2ZV09YB23QDHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSWXDM0YR37VFMPEW43</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
+          <t>h_01M07XPBSZZAW2ZV09YB23QDHR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBSZZAW2ZV09YB23QDHR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,32 +1089,54 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+          <t>h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYTF39ZXBHJWATBR5CF4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M07XPBT6CHP3J1R72QFFA8VE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01M0AAEYTQZDBVE2XPYEPS1WKS</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Homecare-Homebase-Integration-Guide/#h_01M0AAEYTQZDBVE2XPYEPS1WKS</t>
         </is>
